--- a/operations.xlsx
+++ b/operations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -652,9 +652,32 @@
         <v>37584949.97</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>٧‏/٣‏/٢٠٢٥، ١٠:٢٦:١٤ م</v>
+      </c>
+      <c r="B12">
+        <v>240</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>3</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12" t="str">
+        <v>782013.02</v>
+      </c>
+      <c r="G12" t="str">
+        <v>40664676.88</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/operations.xlsx
+++ b/operations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -675,9 +675,32 @@
         <v>40664676.88</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>٧‏/٣‏/٢٠٢٥، ١٠:٣٦:٤٩ م</v>
+      </c>
+      <c r="B13">
+        <v>200</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13" t="str">
+        <v>674676.54</v>
+      </c>
+      <c r="G13" t="str">
+        <v>35083179.95</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/operations.xlsx
+++ b/operations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -698,9 +698,32 @@
         <v>35083179.95</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>٧‏/٣‏/٢٠٢٥، ١٠:٣٧:٤٧ م</v>
+      </c>
+      <c r="B14">
+        <v>130</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>4</v>
+      </c>
+      <c r="F14" t="str">
+        <v>642354.77</v>
+      </c>
+      <c r="G14" t="str">
+        <v>33402448.27</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/operations.xlsx
+++ b/operations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -721,9 +721,32 @@
         <v>33402448.27</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>٧‏/٣‏/٢٠٢٥، ١٠:٤٣:٠٧ م</v>
+      </c>
+      <c r="B15">
+        <v>13</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>4</v>
+      </c>
+      <c r="F15" t="str">
+        <v>548135.04</v>
+      </c>
+      <c r="G15" t="str">
+        <v>28503022.27</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G15"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/operations.xlsx
+++ b/operations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -744,9 +744,32 @@
         <v>28503022.27</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>٨‏/٣‏/٢٠٢٥، ١١:٤٨:٠٤ ص</v>
+      </c>
+      <c r="B16">
+        <v>300</v>
+      </c>
+      <c r="C16">
+        <v>3</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <v>9</v>
+      </c>
+      <c r="F16" t="str">
+        <v>760391.10</v>
+      </c>
+      <c r="G16" t="str">
+        <v>39540337.42</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G16"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/operations.xlsx
+++ b/operations.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Operations" sheetId="1" r:id="rId1"/>
+    <sheet name="PermitData" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,379 +397,115 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:H4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>📅 Date &amp; Time</v>
+        <v>Date &amp; Time</v>
       </c>
       <c r="B1" t="str">
-        <v>📏 Area</v>
+        <v>Required construction area (square meters)</v>
       </c>
       <c r="C1" t="str">
-        <v>🛏️ Rooms</v>
+        <v>Building type (1: Residential, 2: Pump Station, 3: Bridge)</v>
       </c>
       <c r="D1" t="str">
-        <v>🚿 Bathrooms</v>
+        <v>Number of allowed floors</v>
       </c>
       <c r="E1" t="str">
-        <v>📅 Age</v>
+        <v>Permit duration (years)</v>
       </c>
       <c r="F1" t="str">
-        <v>💲 Price (USD)</v>
+        <v>Distance from nearest waterway (meters)</v>
       </c>
       <c r="G1" t="str">
-        <v>💰 Price (EGP)</v>
+        <v>Estimated house price (USD)</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Estimated house price (EGP)</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>٧‏/٣‏/٢٠٢٥، ٩:١٨:٢٢ م</v>
+        <v>2025-03-08 21:32:41</v>
       </c>
       <c r="B2">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E2">
         <v>10</v>
       </c>
-      <c r="F2" t="str">
-        <v>627597.22</v>
+      <c r="F2">
+        <v>100</v>
       </c>
       <c r="G2" t="str">
-        <v>32635055.69</v>
+        <v>90280.44</v>
+      </c>
+      <c r="H2" t="str">
+        <v>4694582.64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>٧‏/٣‏/٢٠٢٥، ٩:٢٠:٤٩ م</v>
+        <v>2025-03-08 21:37:58</v>
       </c>
       <c r="B3">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="C3">
         <v>3</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" t="str">
-        <v>835010.70</v>
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>60</v>
       </c>
       <c r="G3" t="str">
-        <v>43420556.16</v>
+        <v>72485.95</v>
+      </c>
+      <c r="H3" t="str">
+        <v>3769269.61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>٧‏/٣‏/٢٠٢٥، ٩:٢١:١٣ م</v>
+        <v>2025-03-08 21:40:27</v>
       </c>
       <c r="B4">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
-      <c r="F4" t="str">
-        <v>719800.57</v>
+      <c r="F4">
+        <v>100</v>
       </c>
       <c r="G4" t="str">
-        <v>37429629.83</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>٧‏/٣‏/٢٠٢٥، ٩:٢١:٣٢ م</v>
-      </c>
-      <c r="B5">
-        <v>100</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5" t="str">
-        <v>635476.12</v>
-      </c>
-      <c r="G5" t="str">
-        <v>33044758.46</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>٧‏/٣‏/٢٠٢٥، ٩:٢١:٥٢ م</v>
-      </c>
-      <c r="B6">
-        <v>270</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6" t="str">
-        <v>737231.66</v>
-      </c>
-      <c r="G6" t="str">
-        <v>38336046.31</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>٧‏/٣‏/٢٠٢٥، ٩:٢٥:٤١ م</v>
-      </c>
-      <c r="B7">
-        <v>200</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>7</v>
-      </c>
-      <c r="F7" t="str">
-        <v>697035.50</v>
-      </c>
-      <c r="G7" t="str">
-        <v>36245846.18</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>٧‏/٣‏/٢٠٢٥، ٩:٤٣:١٩ م</v>
-      </c>
-      <c r="B8">
-        <v>250</v>
-      </c>
-      <c r="C8">
-        <v>4</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>3</v>
-      </c>
-      <c r="F8" t="str">
-        <v>735367.01</v>
-      </c>
-      <c r="G8" t="str">
-        <v>38239084.32</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>٧‏/٣‏/٢٠٢٥، ٩:٤٤:٢٧ م</v>
-      </c>
-      <c r="B9">
-        <v>100</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
-      <c r="F9" t="str">
-        <v>615187.07</v>
-      </c>
-      <c r="G9" t="str">
-        <v>31989727.78</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>٧‏/٣‏/٢٠٢٥، ٩:٤٤:٥٥ م</v>
-      </c>
-      <c r="B10">
-        <v>200</v>
-      </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10">
-        <v>2</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10" t="str">
-        <v>588710.99</v>
-      </c>
-      <c r="G10" t="str">
-        <v>30612971.35</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>٧‏/٣‏/٢٠٢٥، ١٠:١١:٢٢ م</v>
-      </c>
-      <c r="B11">
-        <v>300</v>
-      </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-      <c r="D11">
-        <v>3</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11" t="str">
-        <v>722787.50</v>
-      </c>
-      <c r="G11" t="str">
-        <v>37584949.97</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>٧‏/٣‏/٢٠٢٥، ١٠:٢٦:١٤ م</v>
-      </c>
-      <c r="B12">
-        <v>240</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-      <c r="D12">
-        <v>3</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12" t="str">
-        <v>782013.02</v>
-      </c>
-      <c r="G12" t="str">
-        <v>40664676.88</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>٧‏/٣‏/٢٠٢٥، ١٠:٣٦:٤٩ م</v>
-      </c>
-      <c r="B13">
-        <v>200</v>
-      </c>
-      <c r="C13">
-        <v>3</v>
-      </c>
-      <c r="D13">
-        <v>2</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13" t="str">
-        <v>674676.54</v>
-      </c>
-      <c r="G13" t="str">
-        <v>35083179.95</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>٧‏/٣‏/٢٠٢٥، ١٠:٣٧:٤٧ م</v>
-      </c>
-      <c r="B14">
-        <v>130</v>
-      </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>4</v>
-      </c>
-      <c r="F14" t="str">
-        <v>642354.77</v>
-      </c>
-      <c r="G14" t="str">
-        <v>33402448.27</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>٧‏/٣‏/٢٠٢٥، ١٠:٤٣:٠٧ م</v>
-      </c>
-      <c r="B15">
-        <v>13</v>
-      </c>
-      <c r="C15">
-        <v>2</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15">
-        <v>4</v>
-      </c>
-      <c r="F15" t="str">
-        <v>548135.04</v>
-      </c>
-      <c r="G15" t="str">
-        <v>28503022.27</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>٨‏/٣‏/٢٠٢٥، ١١:٤٨:٠٤ ص</v>
-      </c>
-      <c r="B16">
-        <v>300</v>
-      </c>
-      <c r="C16">
-        <v>3</v>
-      </c>
-      <c r="D16">
-        <v>2</v>
-      </c>
-      <c r="E16">
-        <v>9</v>
-      </c>
-      <c r="F16" t="str">
-        <v>760391.10</v>
-      </c>
-      <c r="G16" t="str">
-        <v>39540337.42</v>
+        <v>86722.94</v>
+      </c>
+      <c r="H4" t="str">
+        <v>4509592.72</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
   </ignoredErrors>
 </worksheet>
 </file>